--- a/Documents/01-Planning-Budget/Bon de commande.xlsx
+++ b/Documents/01-Planning-Budget/Bon de commande.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurclaret/Documents/Ecole ingé/5A/Projet Dekhli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurclaret/Documents/Ecole ingé/5A/Projet Dekhli/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E15319C-FB5F-9047-8341-509A93F2C186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{978116E7-09CA-C74D-ABD7-C14A26505C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{3E6CBBB9-0284-A04A-A5B8-A4D51BBE38D4}"/>
   </bookViews>
   <sheets>
     <sheet name="BDC" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="158">
   <si>
     <t>Bon de commande</t>
   </si>
@@ -378,6 +378,141 @@
   </si>
   <si>
     <t>https://jlcpcb.com/partdetail/C22775</t>
+  </si>
+  <si>
+    <t>C32843</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/WIZNET-W5500/C32843</t>
+  </si>
+  <si>
+    <t>W5500</t>
+  </si>
+  <si>
+    <t>C12074</t>
+  </si>
+  <si>
+    <t>HR911105A</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/12651-HR911105A/C12074</t>
+  </si>
+  <si>
+    <t>FB (Ferrite Bead) 120R / 25% / 0805</t>
+  </si>
+  <si>
+    <t>C41330</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/42314-CBG201209U121T/C41330</t>
+  </si>
+  <si>
+    <t>C2149071</t>
+  </si>
+  <si>
+    <t>Quartz 25 MHz</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/JYJE-3TJ425000XYFBC/C2149071</t>
+  </si>
+  <si>
+    <t>C21189</t>
+  </si>
+  <si>
+    <t>Résistance 0R / 1 % / 0603</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/21903-0603WAF0000T5E/C21189</t>
+  </si>
+  <si>
+    <t>C23185</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/23912-0603WAF499JT5E/C23185</t>
+  </si>
+  <si>
+    <t>Résistance 49R9 / 1 % / 0603</t>
+  </si>
+  <si>
+    <t>C109318</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-RC0603FR0710RL/C109318</t>
+  </si>
+  <si>
+    <t>Résistance 10R / 1 % / 0603</t>
+  </si>
+  <si>
+    <t>C21122</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/21834-CL10B223KB8NNNC/C21122</t>
+  </si>
+  <si>
+    <t>Condensateur 22 nF / 10 % / 0603</t>
+  </si>
+  <si>
+    <t>C107097</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-CC0603KRX7R9BB682/C107097</t>
+  </si>
+  <si>
+    <t>Condensateur 6.8 nF / 10 % / 0805</t>
+  </si>
+  <si>
+    <t>C49254170</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/CHANGLONG-CL0603FN330RP/C49254170</t>
+  </si>
+  <si>
+    <t>Résistance 330R / 1 % / 0603</t>
+  </si>
+  <si>
+    <t>C49326600</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/AIDECAPACITOR-0603X7R103J500NT/C49326600</t>
+  </si>
+  <si>
+    <t>Condensateur 10 nF / 10 % / 0805</t>
+  </si>
+  <si>
+    <t>C137798</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-RC0603FR0712K4L/C137798</t>
+  </si>
+  <si>
+    <t>Résistance 12.4 K / 1 % / 0603</t>
+  </si>
+  <si>
+    <t>C4520X7R3D102K130KA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.fr/fr/products/detail/tdk/C4520X7R3D102K130KA/789780?s=N4IgTCBcDaIMIBYCsYAMANA7AJQMwBEBGVMAaUN1VIEEQBdAXyA</t>
+  </si>
+  <si>
+    <t>Condensateur céramique CMS / 1nF / 10 % / 2 kV / 1808</t>
+  </si>
+  <si>
+    <t>C92670</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/93863-0603CG270J500NT/C92670</t>
+  </si>
+  <si>
+    <t>Condensateur 27pF / 5 % / 0603</t>
+  </si>
+  <si>
+    <t>C22935</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/23662-0603WAF1004T5E/C22935</t>
+  </si>
+  <si>
+    <t>Résistance 1M / 1 % / 0603</t>
   </si>
 </sst>
 </file>
@@ -387,7 +522,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;_);[Red]\(#,##0.00\ &quot;€&quot;\)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -474,6 +609,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF18181A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111111"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -600,30 +741,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -634,63 +765,98 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -698,7 +864,250 @@
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBFF79"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -716,33 +1125,33 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -765,21 +1174,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -801,37 +1210,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <fgColor rgb="FF7030A0"/>
@@ -841,6 +1219,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFBFF79"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1169,12 +1552,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DE0C87-6541-0143-8A2D-56918BC21942}">
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="7" width="19.33203125" customWidth="1"/>
     <col min="11" max="11" width="11.83203125" customWidth="1"/>
@@ -1183,24 +1566,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="V1" s="6" t="s">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="V1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1241,14 +1624,14 @@
       <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="44" t="s">
+      <c r="O2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44" t="s">
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="44"/>
+      <c r="R2" s="39"/>
       <c r="V2" t="s">
         <v>5</v>
       </c>
@@ -1263,10 +1646,10 @@
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="54" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="3">
@@ -1275,7 +1658,7 @@
       <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="35">
         <v>2</v>
       </c>
       <c r="H3" s="4">
@@ -1296,13 +1679,13 @@
       <c r="L3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="42">
-        <f>(SUM(J3:J37))</f>
-        <v>102.78</v>
-      </c>
-      <c r="R3" s="42"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="43">
+        <f>(SUM(J4:J56))</f>
+        <v>89.439999999999984</v>
+      </c>
+      <c r="R3" s="43"/>
       <c r="V3" t="s">
         <v>6</v>
       </c>
@@ -1317,10 +1700,10 @@
       <c r="B4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="54" t="s">
         <v>53</v>
       </c>
       <c r="E4" s="3">
@@ -1329,16 +1712,16 @@
       <c r="F4" s="3">
         <v>0</v>
       </c>
-      <c r="G4" s="9"/>
+      <c r="G4" s="35"/>
       <c r="H4" s="4">
         <v>4.91</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I32" si="0">((E4-F4)*H4)</f>
+        <f t="shared" ref="I4:I25" si="0">((E4-F4)*H4)</f>
         <v>4.91</v>
       </c>
       <c r="J4" s="4">
-        <f t="shared" ref="J4:J37" si="1">I4*$G$3</f>
+        <f t="shared" ref="J4:J56" si="1">I4*$G$3</f>
         <v>9.82</v>
       </c>
       <c r="K4" s="4">
@@ -1348,10 +1731,10 @@
       <c r="L4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="45"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
       <c r="V4" t="s">
         <v>12</v>
       </c>
@@ -1360,51 +1743,51 @@
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="13">
-        <v>1</v>
-      </c>
-      <c r="F5" s="19">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="23">
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13">
+        <v>0</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="17">
         <v>1.9</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="14">
         <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="14">
         <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="36">
         <f>(J5+J6+J7)</f>
         <v>3.86</v>
       </c>
-      <c r="L5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="44" t="s">
+      <c r="L5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44" t="s">
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="R5" s="44"/>
+      <c r="R5" s="39"/>
       <c r="V5" t="s">
         <v>7</v>
       </c>
@@ -1413,47 +1796,47 @@
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="18">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I6" s="29">
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="4">
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="K6" s="31"/>
+      <c r="K6" s="37"/>
       <c r="L6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="45"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="43">
-        <f>(SUM(E3:E37))</f>
-        <v>43</v>
-      </c>
-      <c r="R6" s="43"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="42">
+        <f>(SUM(E4:E56))</f>
+        <v>73</v>
+      </c>
+      <c r="R6" s="42"/>
       <c r="V6" t="s">
         <v>13</v>
       </c>
@@ -1462,73 +1845,73 @@
       </c>
     </row>
     <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="15">
-        <v>1</v>
-      </c>
-      <c r="F7" s="28">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="21">
-        <v>0.01</v>
-      </c>
-      <c r="I7" s="32">
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0</v>
+      </c>
+      <c r="G7" s="35"/>
+      <c r="H7" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="22">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="22">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K7" s="33"/>
+      <c r="K7" s="38"/>
       <c r="L7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="45"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="8">
         <v>4</v>
       </c>
-      <c r="F8" s="19">
-        <v>1</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="20">
+      <c r="F8" s="13">
+        <v>1</v>
+      </c>
+      <c r="G8" s="35"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="14">
         <v>13.99</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="14">
         <v>13.99</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="36">
         <f>(SUM(J8:J9))</f>
         <v>13.99</v>
       </c>
@@ -1537,73 +1920,73 @@
       </c>
     </row>
     <row r="9" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="15">
-        <v>1</v>
-      </c>
-      <c r="F9" s="28">
-        <v>1</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="21">
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1</v>
+      </c>
+      <c r="G9" s="35"/>
+      <c r="H9" s="15">
         <v>0.04</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="33"/>
+      <c r="J9" s="22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="38"/>
       <c r="L9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="13">
-        <v>1</v>
-      </c>
-      <c r="F10" s="19">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="23">
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="35"/>
+      <c r="H10" s="17">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="36">
         <f>(SUM(J10:J14))</f>
         <v>26.660000000000004</v>
       </c>
@@ -1612,179 +1995,179 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="10">
-        <v>1</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="22">
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="35"/>
+      <c r="H11" s="16">
         <v>0.15</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="4">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="4">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="K11" s="31"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="10">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="22">
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="35"/>
+      <c r="H12" s="16">
         <v>16.260000000000002</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="4">
         <v>16.260000000000002</v>
       </c>
-      <c r="J12" s="29">
+      <c r="J12" s="4">
         <v>16.260000000000002</v>
       </c>
-      <c r="K12" s="31"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="18">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I13" s="29">
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="35"/>
+      <c r="H13" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="4">
         <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="4">
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="K13" s="31"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="15">
-        <v>1</v>
-      </c>
-      <c r="F14" s="28">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="21">
+      <c r="E14" s="10">
+        <v>1</v>
+      </c>
+      <c r="F14" s="21">
+        <v>0</v>
+      </c>
+      <c r="G14" s="35"/>
+      <c r="H14" s="15">
         <v>0.13</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="22">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="22">
         <f t="shared" si="1"/>
         <v>0.26</v>
       </c>
-      <c r="K14" s="33"/>
+      <c r="K14" s="38"/>
       <c r="L14" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="13">
-        <v>1</v>
-      </c>
-      <c r="F15" s="19">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="23">
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13">
+        <v>0</v>
+      </c>
+      <c r="G15" s="35"/>
+      <c r="H15" s="17">
         <v>1.68</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
         <v>1.68</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="14">
         <f t="shared" si="1"/>
         <v>3.36</v>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="36">
         <f>(SUM(J15:J19))</f>
         <v>3.46</v>
       </c>
@@ -1793,181 +2176,181 @@
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="F16" s="18">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I16" s="29">
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="35"/>
+      <c r="H16" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I16" s="4">
         <f t="shared" ref="I16" si="2">((E16-F16)*H16)</f>
         <v>0.02</v>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="4">
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="K16" s="31"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="10">
-        <v>1</v>
-      </c>
-      <c r="F17" s="18">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I17" s="29">
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="35"/>
+      <c r="H17" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="4">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="4">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K17" s="31"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="10">
-        <v>1</v>
-      </c>
-      <c r="F18" s="18">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I18" s="29">
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35"/>
+      <c r="H18" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I18" s="4">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="4">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K18" s="31"/>
+      <c r="K18" s="37"/>
       <c r="L18" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="15">
-        <v>1</v>
-      </c>
-      <c r="F19" s="28">
-        <v>0</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="21">
-        <v>0.01</v>
-      </c>
-      <c r="I19" s="32">
+      <c r="E19" s="10">
+        <v>1</v>
+      </c>
+      <c r="F19" s="21">
+        <v>0</v>
+      </c>
+      <c r="G19" s="35"/>
+      <c r="H19" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="I19" s="22">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="J19" s="32">
+      <c r="J19" s="22">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K19" s="33"/>
+      <c r="K19" s="38"/>
       <c r="L19" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="13">
-        <v>1</v>
-      </c>
-      <c r="F20" s="19">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="23">
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35"/>
+      <c r="H20" s="17">
         <v>0.08</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="14">
         <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="36">
         <f>(SUM(J20:J25))</f>
         <v>3.26</v>
       </c>
@@ -1976,217 +2359,217 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="10">
-        <v>1</v>
-      </c>
-      <c r="F21" s="18">
-        <v>0</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="22">
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35"/>
+      <c r="H21" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="4">
         <f t="shared" si="0"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="4">
         <f t="shared" si="1"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="K21" s="31"/>
+      <c r="K21" s="37"/>
       <c r="L21" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="10">
-        <v>1</v>
-      </c>
-      <c r="F22" s="18">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="22">
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35"/>
+      <c r="H22" s="16">
         <v>0.06</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="4">
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="4">
         <f t="shared" si="1"/>
         <v>0.12</v>
       </c>
-      <c r="K22" s="31"/>
+      <c r="K22" s="37"/>
       <c r="L22" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="10">
-        <v>1</v>
-      </c>
-      <c r="F23" s="18">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I23" s="29">
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35"/>
+      <c r="H23" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I23" s="4">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="4">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K23" s="31"/>
+      <c r="K23" s="37"/>
       <c r="L23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="10">
-        <v>1</v>
-      </c>
-      <c r="F24" s="18">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I24" s="29">
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="12">
+        <v>0</v>
+      </c>
+      <c r="G24" s="35"/>
+      <c r="H24" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I24" s="4">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="4">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K24" s="31"/>
+      <c r="K24" s="37"/>
       <c r="L24" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="15">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="22">
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="21">
+        <v>0</v>
+      </c>
+      <c r="G25" s="35"/>
+      <c r="H25" s="16">
         <v>1.4</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="4">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="4">
         <f t="shared" si="1"/>
         <v>2.8</v>
       </c>
-      <c r="K25" s="31"/>
+      <c r="K25" s="37"/>
       <c r="L25" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="13">
-        <v>1</v>
-      </c>
-      <c r="F26" s="19">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="23">
+      <c r="E26" s="8">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0</v>
+      </c>
+      <c r="G26" s="35"/>
+      <c r="H26" s="17">
         <v>1.4</v>
       </c>
-      <c r="I26" s="20">
-        <f t="shared" ref="I26:I37" si="3">((E26-F26)*H26)</f>
+      <c r="I26" s="14">
+        <f t="shared" ref="I26:I56" si="3">((E26-F26)*H26)</f>
         <v>1.4</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
         <v>2.8</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="36">
         <f>(SUM(J26:J29))</f>
         <v>3.34</v>
       </c>
@@ -2195,144 +2578,144 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="3">
         <v>2</v>
       </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="22">
+      <c r="F27" s="12">
+        <v>0</v>
+      </c>
+      <c r="G27" s="35"/>
+      <c r="H27" s="16">
         <v>0.12</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="4">
         <f t="shared" si="3"/>
         <v>0.24</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="4">
         <f t="shared" si="1"/>
         <v>0.48</v>
       </c>
-      <c r="K27" s="31"/>
+      <c r="K27" s="37"/>
       <c r="L27" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="3">
         <v>2</v>
       </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="I28" s="29">
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="35"/>
+      <c r="H28" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I28" s="4">
         <f t="shared" si="3"/>
         <v>0.02</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="4">
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="K28" s="31"/>
+      <c r="K28" s="37"/>
       <c r="L28" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="15">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="21">
-        <v>0.01</v>
-      </c>
-      <c r="I29" s="32">
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+      <c r="F29" s="21">
+        <v>0</v>
+      </c>
+      <c r="G29" s="35"/>
+      <c r="H29" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="I29" s="22">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="J29" s="32">
+      <c r="J29" s="22">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K29" s="33"/>
+      <c r="K29" s="38"/>
       <c r="L29" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="48">
+      <c r="D30" s="53">
         <v>25743</v>
       </c>
-      <c r="E30" s="13">
-        <v>1</v>
-      </c>
-      <c r="F30" s="19">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="23">
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="35"/>
+      <c r="H30" s="17">
         <v>12.99</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="14">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="14">
         <v>12.99</v>
       </c>
-      <c r="K30" s="49">
+      <c r="K30" s="32">
         <f>(SUM(J30:J31))</f>
         <v>12.99</v>
       </c>
@@ -2341,73 +2724,73 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="15">
-        <v>1</v>
-      </c>
-      <c r="F31" s="28">
-        <v>1</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="21">
+      <c r="E31" s="49">
+        <v>1</v>
+      </c>
+      <c r="F31" s="12">
+        <v>1</v>
+      </c>
+      <c r="G31" s="35"/>
+      <c r="H31" s="16">
         <v>0.05</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="32">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="50"/>
+      <c r="J31" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="34"/>
       <c r="L31" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="13">
-        <v>1</v>
-      </c>
-      <c r="F32" s="19">
-        <v>0</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="23">
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0</v>
+      </c>
+      <c r="G32" s="35"/>
+      <c r="H32" s="17">
         <v>0.21</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="14">
         <f t="shared" si="3"/>
         <v>0.21</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="14">
         <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
-      <c r="K32" s="49">
+      <c r="K32" s="32">
         <f>(SUM(J32:J37))</f>
         <v>0.70000000000000007</v>
       </c>
@@ -2416,134 +2799,134 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="51">
-        <v>1</v>
-      </c>
-      <c r="F33" s="54">
-        <v>0</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="58">
+      <c r="E33" s="49">
+        <v>1</v>
+      </c>
+      <c r="F33" s="12">
+        <v>0</v>
+      </c>
+      <c r="G33" s="35"/>
+      <c r="H33" s="16">
         <v>0.09</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="52">
         <f t="shared" si="3"/>
         <v>0.09</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J33" s="52">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="K33" s="59"/>
+      <c r="K33" s="34"/>
       <c r="L33" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="10">
-        <v>1</v>
-      </c>
-      <c r="F34" s="18">
-        <v>0</v>
-      </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="58">
-        <v>0.01</v>
-      </c>
-      <c r="I34" s="29">
+      <c r="E34" s="49">
+        <v>1</v>
+      </c>
+      <c r="F34" s="12">
+        <v>0</v>
+      </c>
+      <c r="G34" s="35"/>
+      <c r="H34" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I34" s="52">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J34" s="52">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K34" s="59"/>
+      <c r="K34" s="34"/>
       <c r="L34" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="10">
-        <v>1</v>
-      </c>
-      <c r="F35" s="18">
-        <v>0</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="58">
-        <v>0.01</v>
-      </c>
-      <c r="I35" s="29">
+      <c r="E35" s="49">
+        <v>1</v>
+      </c>
+      <c r="F35" s="12">
+        <v>0</v>
+      </c>
+      <c r="G35" s="35"/>
+      <c r="H35" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="I35" s="52">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="J35" s="29">
+      <c r="J35" s="52">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K35" s="59"/>
+      <c r="K35" s="34"/>
       <c r="L35" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="E36" s="51">
-        <v>1</v>
-      </c>
-      <c r="F36" s="54">
-        <v>0</v>
-      </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="58">
+      <c r="E36" s="49">
+        <v>1</v>
+      </c>
+      <c r="F36" s="12">
+        <v>0</v>
+      </c>
+      <c r="G36" s="35"/>
+      <c r="H36" s="16">
         <v>0.02</v>
       </c>
       <c r="I36" s="52">
@@ -2554,73 +2937,761 @@
         <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
-      <c r="K36" s="59"/>
+      <c r="K36" s="34"/>
       <c r="L36" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D37" s="56" t="s">
+      <c r="D37" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="55">
-        <v>1</v>
-      </c>
-      <c r="F37" s="57">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="60">
-        <v>0.01</v>
-      </c>
-      <c r="I37" s="61">
+      <c r="E37" s="10">
+        <v>1</v>
+      </c>
+      <c r="F37" s="21">
+        <v>0</v>
+      </c>
+      <c r="G37" s="35"/>
+      <c r="H37" s="15">
+        <v>0.01</v>
+      </c>
+      <c r="I37" s="22">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="J37" s="61">
+      <c r="J37" s="22">
         <f t="shared" si="1"/>
         <v>0.02</v>
       </c>
-      <c r="K37" s="50"/>
+      <c r="K37" s="33"/>
       <c r="L37" s="3" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="61">
+        <v>1</v>
+      </c>
+      <c r="F38" s="63">
+        <v>0</v>
+      </c>
+      <c r="G38" s="35"/>
+      <c r="H38" s="67">
+        <v>2.83</v>
+      </c>
+      <c r="I38" s="68">
+        <f t="shared" si="3"/>
+        <v>2.83</v>
+      </c>
+      <c r="J38" s="68">
+        <f t="shared" si="1"/>
+        <v>5.66</v>
+      </c>
+      <c r="K38" s="32">
+        <f>(SUM(J38:J56))</f>
+        <v>11.359999999999994</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="45">
+        <v>1</v>
+      </c>
+      <c r="F39" s="46">
+        <v>0</v>
+      </c>
+      <c r="G39" s="35"/>
+      <c r="H39" s="47">
+        <v>1.71</v>
+      </c>
+      <c r="I39" s="48">
+        <f t="shared" si="3"/>
+        <v>1.71</v>
+      </c>
+      <c r="J39" s="48">
+        <f t="shared" si="1"/>
+        <v>3.42</v>
+      </c>
+      <c r="K39" s="34"/>
+      <c r="L39" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="45">
+        <v>1</v>
+      </c>
+      <c r="F40" s="46">
+        <v>0</v>
+      </c>
+      <c r="G40" s="35"/>
+      <c r="H40" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I40" s="48">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J40" s="48">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K40" s="34"/>
+      <c r="L40" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="45">
+        <v>1</v>
+      </c>
+      <c r="F41" s="46">
+        <v>0</v>
+      </c>
+      <c r="G41" s="35"/>
+      <c r="H41" s="47">
+        <v>0.11</v>
+      </c>
+      <c r="I41" s="48">
+        <f t="shared" si="3"/>
+        <v>0.11</v>
+      </c>
+      <c r="J41" s="48">
+        <f t="shared" si="1"/>
+        <v>0.22</v>
+      </c>
+      <c r="K41" s="34"/>
+      <c r="L41" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="49">
+        <v>1</v>
+      </c>
+      <c r="F42" s="12">
+        <v>0</v>
+      </c>
+      <c r="G42" s="35"/>
+      <c r="H42" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I42" s="48">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J42" s="48">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K42" s="34"/>
+      <c r="L42" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="45">
+        <v>5</v>
+      </c>
+      <c r="F43" s="46">
+        <v>0</v>
+      </c>
+      <c r="G43" s="35"/>
+      <c r="H43" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I43" s="48">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+      <c r="J43" s="48">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="K43" s="34"/>
+      <c r="L43" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="49">
+        <v>2</v>
+      </c>
+      <c r="F44" s="12">
+        <v>0</v>
+      </c>
+      <c r="G44" s="35"/>
+      <c r="H44" s="47">
+        <v>0.06</v>
+      </c>
+      <c r="I44" s="48">
+        <f t="shared" si="3"/>
+        <v>0.12</v>
+      </c>
+      <c r="J44" s="48">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="K44" s="34"/>
+      <c r="L44" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="49">
+        <v>4</v>
+      </c>
+      <c r="F45" s="46">
+        <v>0</v>
+      </c>
+      <c r="G45" s="35"/>
+      <c r="H45" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I45" s="48">
+        <f t="shared" si="3"/>
+        <v>0.04</v>
+      </c>
+      <c r="J45" s="48">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+      <c r="K45" s="34"/>
+      <c r="L45" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="49">
+        <v>1</v>
+      </c>
+      <c r="F46" s="46">
+        <v>0</v>
+      </c>
+      <c r="G46" s="35"/>
+      <c r="H46" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I46" s="48">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J46" s="48">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K46" s="34"/>
+      <c r="L46" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" s="49">
+        <v>1</v>
+      </c>
+      <c r="F47" s="46">
+        <v>0</v>
+      </c>
+      <c r="G47" s="35"/>
+      <c r="H47" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I47" s="48">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J47" s="48">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K47" s="34"/>
+      <c r="L47" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D48" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="49">
+        <v>2</v>
+      </c>
+      <c r="F48" s="46">
+        <v>0</v>
+      </c>
+      <c r="G48" s="35"/>
+      <c r="H48" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I48" s="48">
+        <f t="shared" si="3"/>
+        <v>0.02</v>
+      </c>
+      <c r="J48" s="48">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="K48" s="34"/>
+      <c r="L48" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="49">
+        <v>2</v>
+      </c>
+      <c r="F49" s="46">
+        <v>0</v>
+      </c>
+      <c r="G49" s="35"/>
+      <c r="H49" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I49" s="48">
+        <f t="shared" si="3"/>
+        <v>0.02</v>
+      </c>
+      <c r="J49" s="48">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="K49" s="34"/>
+      <c r="L49" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="E50" s="49">
+        <v>2</v>
+      </c>
+      <c r="F50" s="46">
+        <v>0</v>
+      </c>
+      <c r="G50" s="35"/>
+      <c r="H50" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I50" s="48">
+        <f t="shared" si="3"/>
+        <v>0.02</v>
+      </c>
+      <c r="J50" s="48">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="K50" s="34"/>
+      <c r="L50" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="49">
+        <v>1</v>
+      </c>
+      <c r="F51" s="12">
+        <v>0</v>
+      </c>
+      <c r="G51" s="35"/>
+      <c r="H51" s="47">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I51" s="48">
+        <f t="shared" si="3"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J51" s="48">
+        <f t="shared" si="1"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K51" s="34"/>
+      <c r="L51" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="49">
+        <v>1</v>
+      </c>
+      <c r="F52" s="46">
+        <v>0</v>
+      </c>
+      <c r="G52" s="35"/>
+      <c r="H52" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I52" s="48">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J52" s="48">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K52" s="34"/>
+      <c r="L52" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="49">
+        <v>1</v>
+      </c>
+      <c r="F53" s="46">
+        <v>0</v>
+      </c>
+      <c r="G53" s="35"/>
+      <c r="H53" s="47">
+        <v>0.6</v>
+      </c>
+      <c r="I53" s="48">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="J53" s="48">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="K53" s="34"/>
+      <c r="L53" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="49">
+        <v>1</v>
+      </c>
+      <c r="F54" s="12">
+        <v>0</v>
+      </c>
+      <c r="G54" s="35"/>
+      <c r="H54" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I54" s="48">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J54" s="48">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K54" s="34"/>
+      <c r="L54" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E55" s="45">
+        <v>2</v>
+      </c>
+      <c r="F55" s="46">
+        <v>0</v>
+      </c>
+      <c r="G55" s="35"/>
+      <c r="H55" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="I55" s="48">
+        <f t="shared" si="3"/>
+        <v>0.02</v>
+      </c>
+      <c r="J55" s="48">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="K55" s="34"/>
+      <c r="L55" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="65">
+        <v>1</v>
+      </c>
+      <c r="F56" s="66">
+        <v>0</v>
+      </c>
+      <c r="G56" s="35"/>
+      <c r="H56" s="69">
+        <v>0.01</v>
+      </c>
+      <c r="I56" s="70">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="J56" s="70">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="K56" s="33"/>
+      <c r="L56" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="K32:K37"/>
-    <mergeCell ref="G3:G37"/>
-    <mergeCell ref="K26:K29"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O3:P4"/>
-    <mergeCell ref="O6:P7"/>
+  <mergeCells count="19">
+    <mergeCell ref="K38:K56"/>
+    <mergeCell ref="G3:G56"/>
     <mergeCell ref="Q6:R7"/>
     <mergeCell ref="Q3:R4"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="Q5:R5"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="K5:K7"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="K32:K37"/>
+    <mergeCell ref="K26:K29"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O3:P4"/>
+    <mergeCell ref="O6:P7"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="K10:K14"/>
     <mergeCell ref="K15:K19"/>
     <mergeCell ref="K20:K25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A37">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="A3:A52">
+    <cfRule type="cellIs" dxfId="43" priority="32" operator="equal">
       <formula>"Module"</formula>
     </cfRule>
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2632,88 +3703,205 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="44" operator="equal">
+      <formula>"Connecteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="45" operator="equal">
+      <formula>"Capteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="46" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="47" operator="equal">
+      <formula>"Matériel"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="48" operator="equal">
       <formula>"Composant"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A37">
-    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
+  <conditionalFormatting sqref="F3:G3 F4:F56">
+    <cfRule type="cellIs" dxfId="37" priority="39" operator="equal">
+      <formula>"Livré avec défauts"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="40" operator="equal">
+      <formula>"Livré sans défauts"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="41" operator="equal">
+      <formula>"En cours de livraison"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="42" operator="equal">
+      <formula>"Commandé"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="43" operator="equal">
+      <formula>"Non commandé"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L56">
+    <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
+      <formula>"Livré avec défauts"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="35" operator="equal">
+      <formula>"Livré sans défauts"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
+      <formula>"En cours de livraison"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="37" operator="equal">
+      <formula>"Commandé"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="38" operator="equal">
+      <formula>"Non commandé"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="cellIs" dxfId="27" priority="25" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="26">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0DEC3E0D-ED8F-CD4D-91D4-F0CA76EF03A2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
+      <formula>"Connecteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="28" operator="equal">
+      <formula>"Capteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="29" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="30" operator="equal">
       <formula>"Matériel"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="31" operator="equal">
+      <formula>"Composant"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A37">
+  <conditionalFormatting sqref="A55">
+    <cfRule type="cellIs" dxfId="21" priority="18" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8C864B69-1219-6444-92A7-DAB5051CFF67}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
+      <formula>"Connecteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
+      <formula>"Capteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="22" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="23" operator="equal">
+      <formula>"Matériel"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="24" operator="equal">
+      <formula>"Composant"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EB3E9325-19ED-454E-B962-7E8FDB2DC9ED}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
+      <formula>"Connecteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"Capteur"</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
       <formula>"Module"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
+      <formula>"Matériel"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
+      <formula>"Composant"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A37">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+  <conditionalFormatting sqref="A56">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2E8FF13E-D4A8-C048-A76A-CF15B2B86AE7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+      <formula>"Connecteur"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"Capteur"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"Module"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+      <formula>"Matériel"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+      <formula>"Composant"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A37">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+  <conditionalFormatting sqref="A3:A56">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Composant"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Composant"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:A56">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Connecteur"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G3 F4:F37">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
-      <formula>"Non commandé"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G3 F4:F37">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
-      <formula>"Commandé"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G3 F4:F37">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
-      <formula>"En cours de livraison"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G3 F4:F37">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>"Livré sans défauts"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G3 F4:F37">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
-      <formula>"Livré avec défauts"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L37">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
-      <formula>"Non commandé"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L37">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"Commandé"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L37">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
-      <formula>"En cours de livraison"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L37">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"Livré sans défauts"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L37">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"Livré avec défauts"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2" xr:uid="{67E64593-8E98-4441-8C4D-5E19097C1D73}">
       <formula1>$V$2:$V$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A37" xr:uid="{8526C337-B4DF-BF49-B449-735DAB2CC75A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A56" xr:uid="{8526C337-B4DF-BF49-B449-735DAB2CC75A}">
       <formula1>$V$2:$V$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L37" xr:uid="{3AB4FF5A-763E-1240-8D73-C86904B6ED44}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L56" xr:uid="{3AB4FF5A-763E-1240-8D73-C86904B6ED44}">
       <formula1>$W$2:$W$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -2738,6 +3926,25 @@
     <hyperlink ref="C34" r:id="rId18" xr:uid="{7246D0A3-EF36-2F43-B1FE-AE145DFA1833}"/>
     <hyperlink ref="C35" r:id="rId19" xr:uid="{9434585C-616C-3A4C-95FC-A98B17950176}"/>
     <hyperlink ref="C37" r:id="rId20" xr:uid="{A1F18CC2-1136-1C41-A6B1-099BFC7EB499}"/>
+    <hyperlink ref="C38" r:id="rId21" xr:uid="{FD140A6E-B6CA-0044-A0D1-470C301A9FF4}"/>
+    <hyperlink ref="C39" r:id="rId22" xr:uid="{221546D4-0030-F14B-8548-BF6EF4F424DD}"/>
+    <hyperlink ref="C40" r:id="rId23" xr:uid="{162A1FED-A1F6-C942-B289-6336603036BA}"/>
+    <hyperlink ref="C41" r:id="rId24" xr:uid="{233FE657-ADC2-264B-9E1F-D2B614D6701A}"/>
+    <hyperlink ref="C42" r:id="rId25" xr:uid="{B1CB8ECB-90DC-A54F-86A6-AAD0B140642B}"/>
+    <hyperlink ref="C43" r:id="rId26" xr:uid="{03482881-4CFC-284C-87A7-53B73BE03716}"/>
+    <hyperlink ref="C44" r:id="rId27" xr:uid="{DED5255E-4078-4543-BF6C-30497D6AF475}"/>
+    <hyperlink ref="C45" r:id="rId28" xr:uid="{C296D78C-F6A4-EC40-BBCD-AD747E1FBDD5}"/>
+    <hyperlink ref="C46" r:id="rId29" xr:uid="{94E57895-C3E4-B741-B55B-012A03EA0F2D}"/>
+    <hyperlink ref="C47" r:id="rId30" xr:uid="{533568E5-71EE-C94A-AF80-1A7A3D7EC64C}"/>
+    <hyperlink ref="C48" r:id="rId31" xr:uid="{7FF51126-1316-2642-894F-CC81374EEF76}"/>
+    <hyperlink ref="C49" r:id="rId32" xr:uid="{ACA2E367-EAA1-1440-A58C-02C58928AF9F}"/>
+    <hyperlink ref="C50" r:id="rId33" xr:uid="{14F65E17-5AAA-6D42-88AA-3FE521EF4842}"/>
+    <hyperlink ref="C51" r:id="rId34" xr:uid="{0F62B7EB-1F2B-6C41-9AB2-8540F8D978A6}"/>
+    <hyperlink ref="C52" r:id="rId35" xr:uid="{9274453F-976A-9942-9CE4-E4415A16A740}"/>
+    <hyperlink ref="C53" r:id="rId36" xr:uid="{2046916B-B5B6-9647-AA3B-0DA08D6F8CA9}"/>
+    <hyperlink ref="C54" r:id="rId37" xr:uid="{B4E4A95E-F955-0C4A-805B-B54E384810A9}"/>
+    <hyperlink ref="C55" r:id="rId38" xr:uid="{DF9A1215-5DEF-CF45-9154-51F05BFFB2BB}"/>
+    <hyperlink ref="C56" r:id="rId39" xr:uid="{E16065CE-3EE0-6E4E-AA03-72FFFE4C3309}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2754,7 +3961,59 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>A3:A37</xm:sqref>
+          <xm:sqref>A3:A52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0DEC3E0D-ED8F-CD4D-91D4-F0CA76EF03A2}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>A53</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8C864B69-1219-6444-92A7-DAB5051CFF67}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>A55</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EB3E9325-19ED-454E-B962-7E8FDB2DC9ED}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>A54</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2E8FF13E-D4A8-C048-A76A-CF15B2B86AE7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>A56</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
